--- a/Routing_agent/Beat_Planning_Routing_Agent_Cluster_Model.xlsx
+++ b/Routing_agent/Beat_Planning_Routing_Agent_Cluster_Model.xlsx
@@ -8,18 +8,19 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="1. Territory Clustering" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="2. Cumulative BO Scoring" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="3. Route Selection" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="4. Distance vs Output" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="5. Constraints" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="6. Technical Stack" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="7. Illustrative Example" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="8. Evaluation Metrics" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="9. Edge Cases" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="10. Exceptional DC Routing" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="11. Route Distinction Rule" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="0. Alignment vs Config v3" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Overview" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="1. Territory Clustering" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="2. Cumulative BO Scoring" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="3. Route Selection" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="4. Distance vs Output" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="5. Constraints" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="6. Technical Stack" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="7. Illustrative Example" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="8. Evaluation Metrics" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="9. Edge Cases" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="10. Exceptional DC Routing" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="11. Route Distinction Rule" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,190 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="480">
+  <si>
+    <t xml:space="preserve">Alignment Check vs BO_Configuration_Sheet_v3.xlsx (authoritative config)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO_Configuration_Sheet_v3 is the authoritative, business-confirmed parameter source for the Routing Agent (its "Routing Agent - Parameters/Guardrails/Decision Log" sheets, v5 FINAL, all 20 open items closed). Cross-checking it against this workbook surfaced several places where this workbook used illustrative assumptions that turn out to be WRONG or INCOMPLETE relative to the confirmed spec, plus one direct conflict that needs a decision rather than a silent fix. Corrections below have been applied to the relevant sheets; the one conflict is flagged, not auto-resolved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook stated something the authoritative config contradicts — fixed in place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing — added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The authoritative config has a hard rule this workbook never captured — added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflict — flagged, not resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook's own proposal (built earlier in this session) contradicts a confirmed rule — flagged for your decision, not silently overridden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already consistent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook already matched the authoritative config; no change made.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrections Applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This Workbook Said</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authoritative Config Says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet(s) Fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard vs advisory constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook: 80km AND 180min treated together as a combined "hard ceiling."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only travel TIME ≤ 180 min is a hard cap (R1.2, GR-13). Distance (80km/day, 1,600km/month) is ADVISORY ONLY — tracked and shown, but NEVER blocks a route or rejects a plan (R1.5, R1.6, GR-13, OQ-4/13). This was previously documented backwards as a distance floor and has since been corrected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Constraints, 3. Route Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing hard caps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook had no Field_Minutes_Available or task-count cap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field_Minutes_Available = 420 min (7hr field day) is a HARD cap (R1.1, GR-13). Max 5 tasks/day is a HARD ceiling at output, though the achievable number shrinks as real travel time grows toward the 180-min ceiling (R1.4, R1.7, GR-11, GR-R4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Constraints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance calculation method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook: "Haversine as proxy, refined with OR-Tools distance matrix."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haversine × 1.4 circuity factor is the LOCKED PRIMARY per-leg method (R3.1, R3.2). google_distance (whole-shift total) is used only for post-shift QA reconciliation, never a build gate (R0.5, GR-R11).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Technical Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route model naming/count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook: "Route 1/2/3" (Efficiency-Balanced / Score-Max / Distance-Min).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly 3 algorithm-generated models required (R5.1), officially named: Model 1 Priority-Max (OR-Tools Orienteering/Prize-Collecting, no distance cap) / Model 2 Distance-Min-Efficiency (Nearest-Neighbor + 2-opt over Haversine) / Model 3 Balanced-Weighted (Clarke-Wright + 2-opt, alpha-blended 0.4-0.8, default 0.6, alpha derived per-node from historical travel time). Plus an optional Model 4 SE Self-Override (validation-only pass-through).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Route Selection, 7. Illustrative Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Rules — Added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet(s) Updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geo-completeness filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCs with null/invalid coordinates must be excluded pre-generation (GR-R1) — not previously a stated rule here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Edge Cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal-hold exclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal_Hold=TRUE DCs are excluded from every list/output, no exceptions (GR-03, GR-R2, GR-14) — a double-checked, absolute block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trim procedure on time-ceiling breach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-R5: if a route would exceed 180 min given the pool's geography, trim the farthest/lowest-priority stop (ascending Priority_Score) rather than force an over-cap plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Edge Cases, 3. Route Selection (see conflict note below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determinism &amp; logging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same inputs must always produce the same 3 plans (GR-R9/GR-16); every generation run must be logged with inputs/outputs/selection (GR-R10/GR-17).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Edge Cases, 3. Route Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose preservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Routing Agent must never alter a DC's Priority_Score or Matched_Purposes computed upstream — sequencing only (R2.2, GR-R7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflict — Flagged for Your Decision (Not Auto-Resolved)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet "10. Exceptional DC Routing" (built earlier in this session, at your request) proposes: when a DC's own required travel exceeds the standard ceiling, don't truncate — run the FULL BO-tier-priority route uncapped, flagging the overage for monitoring only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The authoritative config's GR-R5 says something different: when a route would exceed the 180-min travel-time ceiling, TRIM stops by ascending Priority_Score (drop the lowest-priority ones first) until it fits — the route is never allowed to exceed the ceiling. Note GR-R5 already protects top-tier BOs the same way our BO Rule intended (lowest priority gets cut first), just via trimming rather than extending the day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I've added a callout directly on sheet "10. Exceptional DC Routing" explaining this conflict rather than silently rewriting your proposal — this is a real business decision (extend the day vs. drop lower-tier BOs) not a factual correction, so it needs your call, not mine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Items From the Authoritative Config (Worth Knowing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg_Speed_Kmph — UNDEFINED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel time = Distance ÷ Avg_Speed_Kmph, but the speed value itself is still open (R3.2: "FILL IN, e.g. 25-30 km/h"). This is flagged as the single most important undefined number in the routing config. All "km" figures used in this workbook's worked examples are therefore illustrative proxies, not yet convertible to the real 180-min time ceiling with confidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance-mismatch threshold — UNDEFINED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-R11 reconciles Haversine×1.4 against real google_distance post-shift, but the acceptable gap threshold is still "[FILL IN, e.g. 20%]".</t>
+  </si>
   <si>
     <t xml:space="preserve">Beat Planning &amp; Routing Agent — Cluster-Based Model</t>
   </si>
@@ -111,9 +295,6 @@
     <t xml:space="preserve">Element</t>
   </si>
   <si>
-    <t xml:space="preserve">Detail</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inputs</t>
   </si>
   <si>
@@ -207,6 +388,9 @@
     <t xml:space="preserve">This converts each cluster into a single comparable "prize" value — how much business value is on offer if this cluster is covered today.</t>
   </si>
   <si>
+    <t xml:space="preserve">Per BO_Configuration_Sheet_v3 (confirmed, reverted): the actual BO_score_i is not a flat tier value — it comes from Section 7's formula: Daily_Priority_Score = 0.40 x Score_Rank1 + 0.35 x Score_Rank2 + 0.25 x Score_Rank3, over the DC's top 3 ranked objectives (out of 5: Private Label, DC Visits, Overall Sales, Outstanding Payments, Long-Term Growth), with a confirmed tie-break order and override rules. The BO1-BO5 tier labels and the 100/80/60/40/20 mapping used in this workbook's worked examples (sheets 7, 10, 11) are simplified illustrative proxies for that formula, not the real scoring mechanism — useful for showing the routing LOGIC clearly, but not a substitute for the actual weighted calculation. Note: this Section 7 ranking logic is explicitly UNCHANGED/reverted — a separate "DC Composite Health Score" (1-100, NRV/GM/Credit/OD-based) exists in the same config but only feeds a different qualification layer (8.5), not this ranking.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stage 3: Route Selection — BO-Score Maximization</t>
   </si>
   <si>
@@ -228,10 +412,10 @@
     <t xml:space="preserve">Subject to</t>
   </si>
   <si>
-    <t xml:space="preserve">Daily travel distance ≤ 80 km; daily travel time ≤ 180 minutes (hard ceiling); minimum dwell time per BO; recency constraints (a BO not visited in n days gets priority weighting).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is modeled as a Prize-Collecting Vehicle Routing / Orienteering Problem, solved using OR-Tools, with route legs sequenced using a Clarke-Wright Savings heuristic as a fast initial solution, refined by OR-Tools' constraint solver for the final feasible sequence.</t>
+    <t xml:space="preserve">CORRECTED: Daily travel TIME &lt;= 180 minutes (HARD ceiling) and total field time &lt;= 420 minutes (HARD); max 5 tasks/day (HARD, nominal ceiling); minimum dwell time per BO; recency constraints. Daily travel DISTANCE (80km) is advisory/informational only and never blocks selection — see sheet "5. Constraints" for the full hard-vs-advisory split.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED naming/count per the authoritative config: a minimum of 3 algorithm-generated models are always run and synced together (R5.1) — Model 1 Priority-Max (OR-Tools Orienteering/Prize-Collecting: maximize sum of Priority_Score x Visited, s.t. Travel&lt;=180min, Travel+Visit&lt;=420min, Visited&lt;=5, no distance cap), Model 2 Distance-Min/Efficiency (Nearest-Neighbor + 2-opt/Or-opt local search over Haversine distances, among the Top-K by Priority_Score), and Model 3 Balanced/Weighted (Clarke-Wright Savings + 2-opt, blended score = alpha x Priority_Captured + (1-alpha) x (1-Travel_Time), alpha derived per-node from historical travel time, bounded 0.4-0.8, default 0.6). An optional Model 4 SE Self-Override allows manual pin/adjustment, validated against guardrails only.</t>
   </si>
   <si>
     <t xml:space="preserve">In practice, the agent does not just pick the highest-CBS cluster in isolation — it evaluates combinations of adjacent clusters that together fit inside the travel budget while jointly maximizing cumulative score, since two medium-value clusters that are close together may beat one high-value cluster that is far away.</t>
@@ -246,13 +430,10 @@
     <t xml:space="preserve">Step</t>
   </si>
   <si>
-    <t xml:space="preserve">Rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Ceiling check (conditional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check whether the DC's own required travel distance/time exceeds 80km / 180 minutes. If it does not, proceed with standard efficiency-ranked selection (Steps 2-4 below). If it does, the DC is reclassified as Exceptional — do NOT exclude it; instead route it using the BO Rule (strict BO-tier priority sequencing, see sheet "10. Exceptional DC Routing") in place of Steps 2-4.</t>
+    <t xml:space="preserve">1. Ceiling check (time-based, HARD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED: check whether the route's cumulative TRAVEL TIME would exceed 180 minutes (the real hard cap) — distance (80km) is advisory only and never triggers this check. If travel time would be exceeded, the authoritative default (GR-R5) is to TRIM stops by ascending Priority_Score (lowest-priority dropped first) until the route fits — see sheet "9. Edge Cases". This workbook's earlier "Exceptional DC / BO Rule" proposal (sheet "10") instead runs the DC uncapped — that is a CONFLICT with GR-R5, flagged on sheet "10" and "0. Alignment vs Config v3" for a decision, not silently resolved here.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Rank by efficiency</t>
@@ -285,6 +466,9 @@
     <t xml:space="preserve">Route Distinction / Beat Cycle: none of the steps above, on their own, guarantee that consecutive routes differ or that every cluster gets a predictable visit cadence — only recency decay (Section 2) provides a soft nudge in that direction. See sheet "11. Route Distinction Rule" for the explicit Repeat-Avoidance and Fixed Rotation models that address this gap.</t>
   </si>
   <si>
+    <t xml:space="preserve">Additional confirmed requirements (BO_Configuration_Sheet_v3): the Routing Agent must never alter the Priority_Score or Matched_Purposes it receives — it only sequences (R2.2, GR-R7). For a fixed candidate pool and date, Models 1-3 must always produce the same 3 plans, with no randomization unless a fixed seed is used (R5.5, GR-R9) — mirrors this workbook's own philosophy in sheet "9. Edge Cases" (Feedback loop oscillation) and "11. Route Distinction Rule" (reproducibility). Every generation run must be logged: which model, what inputs, what output, which plan the SE selected (GR-R10). The SE finalizes plan selection only after that day's punch-in — no fixed cutoff (R5.3, GR-R8).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Objective Function: Minimize Distance vs. Maximize Output</t>
   </si>
   <si>
@@ -315,13 +499,13 @@
     <t xml:space="preserve">This distinction matters operationally: a purely distance-minimizing route will look efficient on a map but may under-deliver on business outcomes; a purely output-maximizing route without a distance constraint is operationally infeasible for a single SE's working day. The model's job is to sit at the efficient frontier between the two — the highest CBS achievable within the hard travel ceiling.</t>
   </si>
   <si>
-    <t xml:space="preserve">Constraints Summary — Conditional Ceiling Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 80km / 180-minute ceiling is applied as a STANDARD constraint, not an absolute one. If a DC's (Distribution Center's) own BO density/spread inherently requires more than 80km or 180 minutes to cover — i.e., the DC itself cannot be served within the standard ceiling — it is reclassified as an Exceptional DC. Exceptional DCs are never dropped or skipped: a route is still generated for them, but routing switches from efficiency-ranked selection to the BO Rule (strict BO-tier priority sequencing). See sheet "10. Exceptional DC Routing" for the full logic.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard Case</t>
+    <t xml:space="preserve">Constraints Summary — Corrected: Time is the Hard Cap, Distance is Advisory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED (per BO_Configuration_Sheet_v3, Routing Agent R1.2/R1.5/R1.6, GR-13): this workbook previously treated an "80km / 180-minute" combined ceiling as the hard constraint. The authoritative config is explicit that only TRAVEL TIME is a hard cap — distance figures are advisory/informational only and never block a route. See "0. Alignment vs Config v3" for the full correction log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD Caps (Route Rejected/Trimmed if Breached)</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint</t>
@@ -330,94 +514,136 @@
     <t xml:space="preserve">Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Enforcement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field_Minutes_Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420 minutes (7-hour field day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD — total time (travel + visits) may never exceed this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-13, R1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max_Travel_Minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 minutes (3-hour ceiling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD — the real travel constraint. If a route would exceed this given the candidate pool's geography, stops are TRIMMED by ascending Priority_Score (lowest-priority dropped first) until it fits — see GR-R5 and sheet "9. Edge Cases"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-13, R1.2, GR-R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max daily tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 tasks/day (nominal ceiling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD upper bound, but the achievable number shrinks as real travel time grows toward the 180-min ceiling — 5 is only reliably hit when travel stays comfortably under cap (see R1.4's worked formula)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-11, GR-R4, R1.4, R1.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADVISORY ONLY (Tracked and Shown, Never Blocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily travel distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 km/day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shown for visibility/cost tracking only — never rejects or trims a route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1.5, GR-13, OQ-4/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly travel distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,600 km/SE/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracked via SUM(google_distance) — informational, flagged to Incentive Policy owner for cost implications, never a build gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1.6, OQ-4/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook's earlier sheets (7, 10, 11) still use an "80km" figure in their worked examples as a simplified illustrative proxy for the time ceiling — this is a simplification, not a claim that distance itself is a real constraint. A proper conversion to minutes needs Avg_Speed_Kmph, which the authoritative config itself flags as still UNDEFINED (R3.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Confirmed Parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purpose</t>
   </si>
   <si>
-    <t xml:space="preserve">Daily travel distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤ 80 km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical/fuel feasibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily travel time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤ 180 minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaves working hours for actual BO visits, not just travel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Minimum dwell time per BO</t>
   </si>
   <si>
-    <t xml:space="preserve">Configurable</t>
+    <t xml:space="preserve">Visit_Duration = 45-60 min</t>
   </si>
   <si>
     <t xml:space="preserve">Ensures visit quality, not just a drive-by</t>
   </si>
   <si>
-    <t xml:space="preserve">Recency decay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prevents permanent starvation of low-density/low-tier clusters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Route selection method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efficiency-ranked (Score-per-km) greedy selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximizes output within the standard budget — see Section 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exceptional Case (Conditional Trigger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC's own required travel distance &gt; 80km, OR required travel time &gt; 180 minutes, to cover its assigned BOs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifies DCs that are structurally too sparse/spread out to fit the standard ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC flagged as "Exceptional DC" for that planning cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separates it from standard optimization so it isn't silently truncated or dropped</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceiling treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard 80km/180min ceiling is not used as a hard cutoff for this DC — it becomes a soft reference point, not a stop condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ensures full BO coverage is still attempted rather than abandoning lower-priority BOs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BO Rule: strict priority sequencing by BO tier (BO1 -&gt; BO2 -&gt; BO3 -&gt; BO4 -&gt; BO5), not Score-per-km efficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guarantees the highest-value BOs are always reached first, even at higher travel cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Route generation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A route is still mandatorily generated for the Exceptional DC — it is never excluded from planning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avoids leaving any DC permanently unserved</t>
+    <t xml:space="preserve">8.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recency decay / visit eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclude if Days_Since_Last_Visit &lt; 5 (independent 2nd pass at routing time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prevents over-frequent contact and permanent starvation of low-density clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haversine x 1.4 circuity factor (locked primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See sheet "6. Technical Stack" for full detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route selection method (standard)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model 1 Priority-Max (primary), cross-checked against Models 2 and 3 — minimum 3 plans always generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximizes output within the HARD time/task caps above — see Section 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4.1-R4.3, R5.1</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Stack Reference</t>
@@ -429,7 +655,7 @@
     <t xml:space="preserve">Distance computation</t>
   </si>
   <si>
-    <t xml:space="preserve">Haversine (first pass) -&gt; OR-Tools distance matrix (road-adjusted)</t>
+    <t xml:space="preserve">CORRECTED: Haversine x 1.4 circuity factor is the LOCKED PRIMARY per-leg method (not a first-pass proxy refined later). google_distance (whole-shift total from the SE app) is used only for post-shift QA reconciliation against the Haversine estimate — monitoring only, never a build gate or route input (R3.1, R3.2, GR-R11).</t>
   </si>
   <si>
     <t xml:space="preserve">Clustering</t>
@@ -438,22 +664,28 @@
     <t xml:space="preserve">Density-aware clustering (k-means/DBSCAN variants) for uniform density-distance partitioning</t>
   </si>
   <si>
-    <t xml:space="preserve">Route construction heuristic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarke-Wright Savings algorithm (fast initial route)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Route optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR-Tools constraint solver, framed as Prize-Collecting VRP / Orienteering Problem</t>
+    <t xml:space="preserve">Route construction heuristics (per model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED/expanded — 3 distinct heuristics per the confirmed models: Model 1 Priority-Max uses OR-Tools Orienteering/Prize-Collecting directly (no separate construction heuristic needed); Model 2 Distance-Min/Efficiency uses Nearest-Neighbor construction + 2-opt/Or-opt local search; Model 3 Balanced/Weighted uses Clarke-Wright Savings + 2-opt, with a per-node alpha blend (0.4-0.8, default 0.6) between priority-captured and travel-time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route optimization (Model 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR-Tools constraint solver, Orienteering/Prize-Collecting formulation: maximize sum(Priority_Score x Visited) subject to Travel_Time&lt;=180min (HARD), Travel+Visit&lt;=420min (HARD), Visited&lt;=5 (HARD). No distance cap in the objective or constraints (R4.1).</t>
   </si>
   <si>
     <t xml:space="preserve">Scoring input</t>
   </si>
   <si>
     <t xml:space="preserve">BO1-BO5 tiering + Focus Product Cohort API (2A -&gt; 2B -&gt; 3 call chain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN — Avg_Speed_Kmph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel_Time_Leg = Distance_Leg / Avg_Speed_Kmph — method confirmed, but the speed value itself is STILL UNDEFINED (flagged as the single most important open number in the routing config; example range given: 25-30 km/h) (R3.2).</t>
   </si>
   <si>
     <t xml:space="preserve">Illustrative Example</t>
@@ -622,9 +854,6 @@
     <t xml:space="preserve">Evaluation Metrics</t>
   </si>
   <si>
-    <t xml:space="preserve">Metric</t>
-  </si>
-  <si>
     <t xml:space="preserve">BO Score Realized / BO Score Available</t>
   </si>
   <si>
@@ -775,13 +1004,58 @@
     <t xml:space="preserve">No explicit rule currently prevents this — recency decay only provides a soft, indirect nudge. Apply the Route Distinction Rule (sheet "11. Route Distinction Rule"): either a Repeat-Avoidance cool-down window, a Fixed Rotation beat calendar, or both layered together.</t>
   </si>
   <si>
+    <t xml:space="preserve">DC has null/invalid geo-coordinates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A candidate DC is missing or has invalid latitude/longitude data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded from ALL plans at the pre-generation filter stage — logged in Dropped_DCs as Geo_Incomplete. Never routed under any circumstance, standard or exceptional (GR-R1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC is under Legal Hold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A candidate DC has an active legal hold flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute exclusion from every list and every agent output, no exceptions — enforced at both pre- and post-generation stages as an independent double-check (GR-03, GR-R2, GR-14).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route would exceed the 180-min travel-time ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given the candidate pool's geography, the route as ranked would need more than 180 minutes of travel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRMED default behavior: trim stops by ascending Priority_Score (lowest-priority dropped first) until the route fits under 180 min — flag Travel_Ceiling_Exceeded and log which stops were dropped and why (GR-R5). See sheet "10. Exceptional DC Routing" for a proposed alternative and the flagged conflict with this rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fewer than 3 distinct feasible plans can be generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The candidate pool is too small or too uniform for Models 1-3 to produce 3 genuinely different plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never silently show fewer than 3 without explanation — flag Insufficient_Candidates_For_3_Plans and show however many are genuinely distinct (GR-R6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-reproducible plan output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same candidate pool and date snapshot produce different plans on repeated runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated as a bug, not acceptable variability — Models 1-3 must be deterministic code, never free-form generation, for a fixed input snapshot (GR-R9, GR-16).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exceptional DC Routing — Conditional Ceiling &amp; the BO Rule</t>
   </si>
   <si>
     <t xml:space="preserve">When a DC Becomes "Exceptional"</t>
   </si>
   <si>
-    <t xml:space="preserve">The 80km / 180-minute ceiling is a STANDARD constraint, applied by default. But some DCs (Distribution Centers) are inherently sparse or geographically spread out — their own assigned BOs cannot be covered within 80km or 180 minutes even before any cross-DC route optimization is applied. Rather than truncating the route and silently dropping lower-ranked BOs (as the standard efficiency-ranked model would), such a DC is reclassified as Exceptional, and a dedicated route is still generated for it — sequenced by the BO Rule instead of Score-per-km.</t>
+    <t xml:space="preserve">The 180-minute travel-time ceiling is the HARD constraint (see sheet "5. Constraints" for the corrected hard-vs-advisory split — distance/80km is advisory only). Some DCs are inherently sparse or spread out — their own assigned BOs cannot be covered within 180 minutes of travel even before any cross-DC optimization is applied. This sheet's proposal: rather than truncating and dropping lower-ranked BOs, reclassify the DC as Exceptional and still generate a full route, sequenced by the BO Rule instead of Score-per-km — see the conflict callout above for how this compares to the authoritative config's GR-R5 (trim, don't extend).</t>
   </si>
   <si>
     <t xml:space="preserve">The BO Rule</t>
@@ -1003,6 +1277,9 @@
     <t xml:space="preserve">Route Distinction / Beat Cycle Rule</t>
   </si>
   <si>
+    <t xml:space="preserve">Note: BO_Configuration_Sheet_v3 (the authoritative Routing Agent config) does not define an explicit route-distinction or beat-cycle rule — it specifies determinism the other way (same inputs must always yield the same 3 plans, GR-R9/R5.5), which is about reproducibility, not forced variation. The two models below remain a proposal from this session, not yet part of the confirmed config — flagging this so it isn't mistaken for an existing system rule.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Today, the only mechanism causing route-to-route variation is recency decay in the BO Scoring stage (Section 2) — a visited cluster's score drops for the next cycle, which indirectly makes it less likely to be picked again immediately. This is a soft, incidental effect, not an explicit rule: nothing currently guarantees that consecutive routes are distinct, and nothing guarantees every cluster gets visited on a predictable cadence. This sheet adds that as an explicit rule, with two alternative models.</t>
   </si>
   <si>
@@ -1028,9 +1305,6 @@
   </si>
   <si>
     <t xml:space="preserve">If excluding it would leave the day's route empty or below a minimum coverage threshold, the cool-down is waived for the single highest-scoring blocked cluster (an escape hatch, not a silent failure).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter</t>
   </si>
   <si>
     <t xml:space="preserve">Cool-down window N is configurable — e.g., N=1 (can't repeat tomorrow) up to N=6 (roughly a weekly rotation).</t>
@@ -1266,9 +1540,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF595959"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1282,15 +1554,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1328,7 +1602,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1337,8 +1611,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FF800000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1355,8 +1629,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1367,14 +1653,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1383,8 +1669,20 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1399,6 +1697,43 @@
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
@@ -1433,169 +1768,229 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1627,12 +2022,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF2E75B6"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D2E9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1642,13 +2037,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1850,11 +2245,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1866,16 +2264,18 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -1886,122 +2286,312 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="7" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="D13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A16:F16"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2018,176 +2608,61 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>243</v>
+      <c r="A3" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -2209,7 +2684,253 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="47" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20"/>
@@ -2229,20 +2950,30 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>245</v>
+        <v>336</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2252,21 +2983,21 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>247</v>
+        <v>338</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2276,61 +3007,62 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>252</v>
+      <c r="A7" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>254</v>
+      <c r="A10" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>256</v>
-      </c>
-    </row>
+      <c r="A11" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2341,543 +3073,547 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
+      <c r="A14" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="R16" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="T16" s="6" t="s">
-        <v>277</v>
+      <c r="A16" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="R16" s="53" t="s">
+        <v>366</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="A17" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="28" t="n">
         <f aca="false">RANK(I17,$I$17:$I$22,1)</f>
         <v>1</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="28" t="n">
         <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D17,$C$17:$C$22)</f>
         <v>12</v>
       </c>
-      <c r="F17" s="18" t="str">
+      <c r="F17" s="28" t="str">
         <f aca="false">IF(E17&gt;80,"Yes — over ceiling","No")</f>
         <v>No</v>
       </c>
-      <c r="G17" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="15" t="n">
+      <c r="G17" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" s="23" t="n">
         <f aca="false">VALUE(MID(B17,3,1))</f>
         <v>1</v>
       </c>
-      <c r="I17" s="20" t="n">
+      <c r="I17" s="28" t="n">
         <f aca="false">H17+C17/10000</f>
         <v>1.0012</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="23" t="n">
         <f aca="false">VLOOKUP(B17,$S$17:$T$21,2,FALSE())</f>
         <v>100</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="25" t="n">
         <f aca="false">IFERROR(J17/C17,0)</f>
         <v>8.33333333333333</v>
       </c>
-      <c r="L17" s="20" t="n">
+      <c r="L17" s="28" t="n">
         <f aca="false">RANK(K17,$K$17:$K$22,0)+COUNTIF($K$17:K17,K17)-1</f>
         <v>1</v>
       </c>
-      <c r="M17" s="20" t="n">
+      <c r="M17" s="28" t="n">
         <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L17,$C$17:$C$22)</f>
         <v>12</v>
       </c>
-      <c r="N17" s="21" t="str">
+      <c r="N17" s="29" t="str">
         <f aca="false">IF(M17&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O17" s="22" t="n">
+      <c r="O17" s="30" t="n">
         <f aca="false">RANK(C17,$C$17:$C$22,1)+COUNTIF($C$17:C17,C17)-1</f>
         <v>3</v>
       </c>
-      <c r="P17" s="22" t="n">
+      <c r="P17" s="30" t="n">
         <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O17,$C$17:$C$22)</f>
         <v>30</v>
       </c>
-      <c r="Q17" s="23" t="str">
+      <c r="Q17" s="31" t="str">
         <f aca="false">IF(P17&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="S17" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="T17" s="24" t="n">
+      <c r="S17" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="T17" s="32" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="A18" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="C18" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="26" t="n">
         <f aca="false">RANK(I18,$I$17:$I$22,1)</f>
         <v>2</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="26" t="n">
         <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D18,$C$17:$C$22)</f>
         <v>37</v>
       </c>
-      <c r="F18" s="18" t="str">
+      <c r="F18" s="26" t="str">
         <f aca="false">IF(E18&gt;80,"Yes — over ceiling","No")</f>
         <v>No</v>
       </c>
-      <c r="G18" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="15" t="n">
+      <c r="G18" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="H18" s="23" t="n">
         <f aca="false">VALUE(MID(B18,3,1))</f>
         <v>1</v>
       </c>
-      <c r="I18" s="20" t="n">
+      <c r="I18" s="28" t="n">
         <f aca="false">H18+C18/10000</f>
         <v>1.0025</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="23" t="n">
         <f aca="false">VLOOKUP(B18,$S$17:$T$21,2,FALSE())</f>
         <v>100</v>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="K18" s="25" t="n">
         <f aca="false">IFERROR(J18/C18,0)</f>
         <v>4</v>
       </c>
-      <c r="L18" s="20" t="n">
+      <c r="L18" s="28" t="n">
         <f aca="false">RANK(K18,$K$17:$K$22,0)+COUNTIF($K$17:K18,K18)-1</f>
         <v>5</v>
       </c>
-      <c r="M18" s="20" t="n">
+      <c r="M18" s="28" t="n">
         <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L18,$C$17:$C$22)</f>
         <v>73</v>
       </c>
-      <c r="N18" s="21" t="str">
+      <c r="N18" s="29" t="str">
         <f aca="false">IF(M18&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O18" s="22" t="n">
+      <c r="O18" s="30" t="n">
         <f aca="false">RANK(C18,$C$17:$C$22,1)+COUNTIF($C$17:C18,C18)-1</f>
         <v>6</v>
       </c>
-      <c r="P18" s="22" t="n">
+      <c r="P18" s="30" t="n">
         <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O18,$C$17:$C$22)</f>
         <v>95</v>
       </c>
-      <c r="Q18" s="23" t="str">
+      <c r="Q18" s="31" t="str">
         <f aca="false">IF(P18&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="S18" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="T18" s="24" t="n">
+      <c r="S18" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="T18" s="32" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="A19" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C19" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="28" t="n">
         <f aca="false">RANK(I19,$I$17:$I$22,1)</f>
         <v>3</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="28" t="n">
         <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D19,$C$17:$C$22)</f>
         <v>55</v>
       </c>
-      <c r="F19" s="18" t="str">
+      <c r="F19" s="28" t="str">
         <f aca="false">IF(E19&gt;80,"Yes — over ceiling","No")</f>
         <v>No</v>
       </c>
-      <c r="G19" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H19" s="15" t="n">
+      <c r="G19" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="H19" s="23" t="n">
         <f aca="false">VALUE(MID(B19,3,1))</f>
         <v>2</v>
       </c>
-      <c r="I19" s="20" t="n">
+      <c r="I19" s="28" t="n">
         <f aca="false">H19+C19/10000</f>
         <v>2.0018</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="23" t="n">
         <f aca="false">VLOOKUP(B19,$S$17:$T$21,2,FALSE())</f>
         <v>80</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="K19" s="25" t="n">
         <f aca="false">IFERROR(J19/C19,0)</f>
         <v>4.44444444444445</v>
       </c>
-      <c r="L19" s="20" t="n">
+      <c r="L19" s="28" t="n">
         <f aca="false">RANK(K19,$K$17:$K$22,0)+COUNTIF($K$17:K19,K19)-1</f>
         <v>4</v>
       </c>
-      <c r="M19" s="20" t="n">
+      <c r="M19" s="28" t="n">
         <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L19,$C$17:$C$22)</f>
         <v>48</v>
       </c>
-      <c r="N19" s="21" t="str">
+      <c r="N19" s="29" t="str">
         <f aca="false">IF(M19&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O19" s="22" t="n">
+      <c r="O19" s="30" t="n">
         <f aca="false">RANK(C19,$C$17:$C$22,1)+COUNTIF($C$17:C19,C19)-1</f>
         <v>4</v>
       </c>
-      <c r="P19" s="22" t="n">
+      <c r="P19" s="30" t="n">
         <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O19,$C$17:$C$22)</f>
         <v>48</v>
       </c>
-      <c r="Q19" s="23" t="str">
+      <c r="Q19" s="31" t="str">
         <f aca="false">IF(P19&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="S19" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="T19" s="24" t="n">
+      <c r="S19" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="T19" s="32" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="A20" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="26" t="n">
         <f aca="false">RANK(I20,$I$17:$I$22,1)</f>
         <v>4</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="26" t="n">
         <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D20,$C$17:$C$22)</f>
         <v>77</v>
       </c>
-      <c r="F20" s="18" t="str">
+      <c r="F20" s="26" t="str">
         <f aca="false">IF(E20&gt;80,"Yes — over ceiling","No")</f>
         <v>No</v>
       </c>
-      <c r="G20" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H20" s="15" t="n">
+      <c r="G20" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="H20" s="23" t="n">
         <f aca="false">VALUE(MID(B20,3,1))</f>
         <v>2</v>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="I20" s="28" t="n">
         <f aca="false">H20+C20/10000</f>
         <v>2.0022</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="23" t="n">
         <f aca="false">VLOOKUP(B20,$S$17:$T$21,2,FALSE())</f>
         <v>80</v>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="K20" s="25" t="n">
         <f aca="false">IFERROR(J20/C20,0)</f>
         <v>3.63636363636364</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="L20" s="28" t="n">
         <f aca="false">RANK(K20,$K$17:$K$22,0)+COUNTIF($K$17:K20,K20)-1</f>
         <v>6</v>
       </c>
-      <c r="M20" s="20" t="n">
+      <c r="M20" s="28" t="n">
         <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L20,$C$17:$C$22)</f>
         <v>95</v>
       </c>
-      <c r="N20" s="21" t="str">
+      <c r="N20" s="29" t="str">
         <f aca="false">IF(M20&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="O20" s="22" t="n">
+      <c r="O20" s="30" t="n">
         <f aca="false">RANK(C20,$C$17:$C$22,1)+COUNTIF($C$17:C20,C20)-1</f>
         <v>5</v>
       </c>
-      <c r="P20" s="22" t="n">
+      <c r="P20" s="30" t="n">
         <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O20,$C$17:$C$22)</f>
         <v>70</v>
       </c>
-      <c r="Q20" s="23" t="str">
+      <c r="Q20" s="31" t="str">
         <f aca="false">IF(P20&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="S20" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="T20" s="24" t="n">
+      <c r="S20" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="T20" s="32" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="A21" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="C21" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="28" t="n">
         <f aca="false">RANK(I21,$I$17:$I$22,1)</f>
         <v>5</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="28" t="n">
         <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D21,$C$17:$C$22)</f>
         <v>87</v>
       </c>
-      <c r="F21" s="18" t="str">
+      <c r="F21" s="28" t="str">
         <f aca="false">IF(E21&gt;80,"Yes — over ceiling","No")</f>
         <v>Yes — over ceiling</v>
       </c>
-      <c r="G21" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="15" t="n">
+      <c r="G21" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="H21" s="23" t="n">
         <f aca="false">VALUE(MID(B21,3,1))</f>
         <v>3</v>
       </c>
-      <c r="I21" s="20" t="n">
+      <c r="I21" s="23" t="n">
         <f aca="false">H21+C21/10000</f>
         <v>3.001</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="23" t="n">
         <f aca="false">VLOOKUP(B21,$S$17:$T$21,2,FALSE())</f>
         <v>60</v>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="K21" s="25" t="n">
         <f aca="false">IFERROR(J21/C21,0)</f>
         <v>6</v>
       </c>
-      <c r="L21" s="20" t="n">
+      <c r="L21" s="28" t="n">
         <f aca="false">RANK(K21,$K$17:$K$22,0)+COUNTIF($K$17:K21,K21)-1</f>
         <v>2</v>
       </c>
-      <c r="M21" s="20" t="n">
+      <c r="M21" s="28" t="n">
         <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L21,$C$17:$C$22)</f>
         <v>22</v>
       </c>
-      <c r="N21" s="21" t="str">
+      <c r="N21" s="29" t="str">
         <f aca="false">IF(M21&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O21" s="22" t="n">
+      <c r="O21" s="30" t="n">
         <f aca="false">RANK(C21,$C$17:$C$22,1)+COUNTIF($C$17:C21,C21)-1</f>
         <v>2</v>
       </c>
-      <c r="P21" s="22" t="n">
+      <c r="P21" s="30" t="n">
         <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O21,$C$17:$C$22)</f>
         <v>18</v>
       </c>
-      <c r="Q21" s="23" t="str">
+      <c r="Q21" s="31" t="str">
         <f aca="false">IF(P21&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="S21" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="T21" s="24" t="n">
+      <c r="S21" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="T21" s="32" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="A22" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="C22" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="28" t="n">
         <f aca="false">RANK(I22,$I$17:$I$22,1)</f>
         <v>6</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="28" t="n">
         <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D22,$C$17:$C$22)</f>
         <v>95</v>
       </c>
-      <c r="F22" s="18" t="str">
+      <c r="F22" s="28" t="str">
         <f aca="false">IF(E22&gt;80,"Yes — over ceiling","No")</f>
         <v>Yes — over ceiling</v>
       </c>
-      <c r="G22" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="15" t="n">
+      <c r="G22" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="H22" s="23" t="n">
         <f aca="false">VALUE(MID(B22,3,1))</f>
         <v>4</v>
       </c>
-      <c r="I22" s="20" t="n">
+      <c r="I22" s="23" t="n">
         <f aca="false">H22+C22/10000</f>
         <v>4.0008</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="23" t="n">
         <f aca="false">VLOOKUP(B22,$S$17:$T$21,2,FALSE())</f>
         <v>40</v>
       </c>
-      <c r="K22" s="17" t="n">
+      <c r="K22" s="25" t="n">
         <f aca="false">IFERROR(J22/C22,0)</f>
         <v>5</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="L22" s="28" t="n">
         <f aca="false">RANK(K22,$K$17:$K$22,0)+COUNTIF($K$17:K22,K22)-1</f>
         <v>3</v>
       </c>
-      <c r="M22" s="20" t="n">
+      <c r="M22" s="28" t="n">
         <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L22,$C$17:$C$22)</f>
         <v>30</v>
       </c>
-      <c r="N22" s="21" t="str">
+      <c r="N22" s="29" t="str">
         <f aca="false">IF(M22&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O22" s="22" t="n">
+      <c r="O22" s="30" t="n">
         <f aca="false">RANK(C22,$C$17:$C$22,1)+COUNTIF($C$17:C22,C22)-1</f>
         <v>1</v>
       </c>
-      <c r="P22" s="22" t="n">
+      <c r="P22" s="30" t="n">
         <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O22,$C$17:$C$22)</f>
         <v>8</v>
       </c>
-      <c r="Q22" s="23" t="str">
+      <c r="Q22" s="31" t="str">
         <f aca="false">IF(P22&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="27" t="n">
+      <c r="A23" s="54" t="s">
+        <v>380</v>
+      </c>
+      <c r="B23" s="54"/>
+      <c r="C23" s="37" t="n">
         <f aca="false">SUM(C17:C22)</f>
         <v>95</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>290</v>
-      </c>
-    </row>
+      <c r="F23" s="39" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
+      <c r="A25" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
+      <c r="A27" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>293</v>
+        <v>384</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2897,136 +3633,145 @@
       <c r="Q29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
+      <c r="A30" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>300</v>
+      <c r="A31" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="D32" s="18" t="str">
+      <c r="A32" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" s="26" t="str">
         <f aca="false">SUMPRODUCT(--(F17:F22="No"))&amp;" of 6"</f>
         <v>4 of 6</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="26" t="n">
         <f aca="false">SUMIF(F17:F22,"No",J17:J22)</f>
         <v>360</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>304</v>
+      <c r="F32" s="9" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="D33" s="20" t="str">
+      <c r="A33" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>397</v>
+      </c>
+      <c r="C33" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="D33" s="28" t="str">
         <f aca="false">SUMPRODUCT(--(N17:N22="Y"))&amp;" of 6"</f>
         <v>5 of 6</v>
       </c>
-      <c r="E33" s="20" t="n">
+      <c r="E33" s="28" t="n">
         <f aca="false">SUMIF(N17:N22,"Y",J17:J22)</f>
         <v>380</v>
       </c>
-      <c r="F33" s="14" t="s">
-        <v>308</v>
+      <c r="F33" s="47" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="D34" s="22" t="str">
+      <c r="A34" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="D34" s="30" t="str">
         <f aca="false">SUMPRODUCT(--(Q17:Q22="Y"))&amp;" of 6"</f>
         <v>5 of 6</v>
       </c>
-      <c r="E34" s="22" t="n">
+      <c r="E34" s="30" t="n">
         <f aca="false">SUMIF(Q17:Q22,"Y",J17:J22)</f>
         <v>360</v>
       </c>
-      <c r="F34" s="37" t="s">
-        <v>312</v>
-      </c>
-    </row>
+      <c r="F34" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-    </row>
+      <c r="A36" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="191.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
@@ -3050,438 +3795,469 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="A1" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="A4" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="A5" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>71</v>
+      <c r="A6" s="52" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>319</v>
+      <c r="A7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>321</v>
+      <c r="A8" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>323</v>
+      <c r="A9" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>325</v>
+      <c r="A10" s="47" t="s">
+        <v>414</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>330</v>
+      <c r="A13" s="52" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>334</v>
+      <c r="A14" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>338</v>
+      <c r="A15" s="47" t="s">
+        <v>422</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>423</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>424</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>341</v>
+      <c r="A16" s="47" t="s">
+        <v>426</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="A20" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>71</v>
+      <c r="A21" s="52" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>345</v>
+      <c r="A22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>346</v>
+      <c r="A23" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="B24" s="37" t="s">
-        <v>348</v>
+      <c r="A24" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>350</v>
+      <c r="A25" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>355</v>
+      <c r="A28" s="52" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="B29" s="37" t="s">
-        <v>356</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>358</v>
+      <c r="A29" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>361</v>
+      <c r="A30" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="C31" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>364</v>
+      <c r="A31" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="B32" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>367</v>
+      <c r="A32" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>372</v>
+      <c r="A36" s="55" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>375</v>
+      <c r="A37" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>378</v>
+      <c r="A38" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>381</v>
+      <c r="A39" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>384</v>
+      <c r="A40" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>387</v>
+      <c r="A41" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+    </row>
+    <row r="44" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="52" t="s">
+        <v>479</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
@@ -3509,6 +4285,174 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A16:F16"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3517,18 +4461,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3537,18 +4481,18 @@
       <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3557,48 +4501,48 @@
       <c r="F5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>26</v>
+      <c r="A6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>28</v>
+      <c r="A7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>30</v>
+      <c r="A8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>32</v>
+      <c r="A9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>34</v>
+      <c r="A10" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3607,45 +4551,45 @@
       <c r="F12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="A13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
+      <c r="A14" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>39</v>
+      <c r="A15" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>41</v>
+      <c r="A16" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>43</v>
+      <c r="A17" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3667,12 +4611,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -3680,28 +4624,28 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3710,18 +4654,18 @@
       <c r="F4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="A5" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -3730,248 +4674,66 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>50</v>
+      <c r="A8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>52</v>
+      <c r="A9" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>54</v>
+      <c r="A10" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>56</v>
+      <c r="A11" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="A13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A13:F13"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3988,6 +4750,210 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3996,52 +4962,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
+      <c r="A4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>87</v>
+      <c r="A5" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>89</v>
+      <c r="A6" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -4050,34 +5016,34 @@
       <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="A9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="A10" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4098,280 +5064,265 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="55"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A12:F12"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>140</v>
+      <c r="B20" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4388,7 +5339,99 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -4404,561 +5447,573 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="A1" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
+      <c r="A3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>159</v>
+      <c r="A5" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="16" t="n">
+      <c r="A6" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="24" t="n">
         <v>92</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">D6+E6</f>
         <v>10</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="25" t="n">
         <f aca="false">IFERROR(C6/F6,0)</f>
         <v>9.2</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="I6" s="18" t="n">
+      <c r="H6" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I6" s="26" t="n">
         <f aca="false">RANK(G6,$G$6:$G$11,0)+COUNTIF($G$6:G6,G6)-1</f>
         <v>2</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="26" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I6,$F$6:$F$11)</f>
         <v>15</v>
       </c>
-      <c r="K6" s="19" t="str">
+      <c r="K6" s="27" t="str">
         <f aca="false">IF(J6&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="L6" s="28" t="n">
         <f aca="false">RANK(C6,$C$6:$C$11,0)+COUNTIF($C$6:C6,C6)-1</f>
         <v>1</v>
       </c>
-      <c r="M6" s="20" t="n">
+      <c r="M6" s="28" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L6,$F$6:$F$11)</f>
         <v>10</v>
       </c>
-      <c r="N6" s="21" t="str">
+      <c r="N6" s="29" t="str">
         <f aca="false">IF(M6&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O6" s="22" t="n">
+      <c r="O6" s="30" t="n">
         <f aca="false">RANK(F6,$F$6:$F$11,1)+COUNTIF($F$6:F6,F6)-1</f>
         <v>3</v>
       </c>
-      <c r="P6" s="22" t="n">
+      <c r="P6" s="30" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O6,$F$6:$F$11)</f>
         <v>23</v>
       </c>
-      <c r="Q6" s="23" t="str">
+      <c r="Q6" s="31" t="str">
         <f aca="false">IF(P6&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="32" t="n">
         <f aca="false">D7+E7</f>
         <v>13</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">IFERROR(C7/F7,0)</f>
         <v>4.69230769230769</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="18" t="n">
+      <c r="H7" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I7" s="26" t="n">
         <f aca="false">RANK(G7,$G$6:$G$11,0)+COUNTIF($G$6:G7,G7)-1</f>
         <v>3</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="26" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I7,$F$6:$F$11)</f>
         <v>28</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="27" t="str">
         <f aca="false">IF(J7&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="L7" s="28" t="n">
         <f aca="false">RANK(C7,$C$6:$C$11,0)+COUNTIF($C$6:C7,C7)-1</f>
         <v>4</v>
       </c>
-      <c r="M7" s="20" t="n">
+      <c r="M7" s="28" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L7,$F$6:$F$11)</f>
         <v>75</v>
       </c>
-      <c r="N7" s="21" t="str">
+      <c r="N7" s="29" t="str">
         <f aca="false">IF(M7&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O7" s="22" t="n">
+      <c r="O7" s="30" t="n">
         <f aca="false">RANK(F7,$F$6:$F$11,1)+COUNTIF($F$6:F7,F7)-1</f>
         <v>4</v>
       </c>
-      <c r="P7" s="22" t="n">
+      <c r="P7" s="30" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O7,$F$6:$F$11)</f>
         <v>36</v>
       </c>
-      <c r="Q7" s="23" t="str">
+      <c r="Q7" s="31" t="str">
         <f aca="false">IF(P7&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="24" t="n">
         <v>78</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">D8+E8</f>
         <v>25</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="25" t="n">
         <f aca="false">IFERROR(C8/F8,0)</f>
         <v>3.12</v>
       </c>
-      <c r="H8" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="I8" s="18" t="n">
+      <c r="H8" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="26" t="n">
         <f aca="false">RANK(G8,$G$6:$G$11,0)+COUNTIF($G$6:G8,G8)-1</f>
         <v>6</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="26" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I8,$F$6:$F$11)</f>
         <v>88</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="27" t="str">
         <f aca="false">IF(J8&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="L8" s="20" t="n">
+      <c r="L8" s="28" t="n">
         <f aca="false">RANK(C8,$C$6:$C$11,0)+COUNTIF($C$6:C8,C8)-1</f>
         <v>3</v>
       </c>
-      <c r="M8" s="20" t="n">
+      <c r="M8" s="28" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L8,$F$6:$F$11)</f>
         <v>62</v>
       </c>
-      <c r="N8" s="21" t="str">
+      <c r="N8" s="29" t="str">
         <f aca="false">IF(M8&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O8" s="22" t="n">
+      <c r="O8" s="30" t="n">
         <f aca="false">RANK(F8,$F$6:$F$11,1)+COUNTIF($F$6:F8,F8)-1</f>
         <v>5</v>
       </c>
-      <c r="P8" s="22" t="n">
+      <c r="P8" s="30" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O8,$F$6:$F$11)</f>
         <v>61</v>
       </c>
-      <c r="Q8" s="23" t="str">
+      <c r="Q8" s="31" t="str">
         <f aca="false">IF(P8&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="32" t="n">
         <f aca="false">D9+E9</f>
         <v>5</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="33" t="n">
         <f aca="false">IFERROR(C9/F9,0)</f>
         <v>11</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="I9" s="18" t="n">
+      <c r="H9" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I9" s="26" t="n">
         <f aca="false">RANK(G9,$G$6:$G$11,0)+COUNTIF($G$6:G9,G9)-1</f>
         <v>1</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="26" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I9,$F$6:$F$11)</f>
         <v>5</v>
       </c>
-      <c r="K9" s="19" t="str">
+      <c r="K9" s="27" t="str">
         <f aca="false">IF(J9&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" s="28" t="n">
         <f aca="false">RANK(C9,$C$6:$C$11,0)+COUNTIF($C$6:C9,C9)-1</f>
         <v>5</v>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" s="28" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L9,$F$6:$F$11)</f>
         <v>80</v>
       </c>
-      <c r="N9" s="21" t="str">
+      <c r="N9" s="29" t="str">
         <f aca="false">IF(M9&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O9" s="22" t="n">
+      <c r="O9" s="30" t="n">
         <f aca="false">RANK(F9,$F$6:$F$11,1)+COUNTIF($F$6:F9,F9)-1</f>
         <v>1</v>
       </c>
-      <c r="P9" s="22" t="n">
+      <c r="P9" s="30" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O9,$F$6:$F$11)</f>
         <v>5</v>
       </c>
-      <c r="Q9" s="23" t="str">
+      <c r="Q9" s="31" t="str">
         <f aca="false">IF(P9&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="24" t="n">
         <v>88</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="23" t="n">
         <f aca="false">D10+E10</f>
         <v>27</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="25" t="n">
         <f aca="false">IFERROR(C10/F10,0)</f>
         <v>3.25925925925926</v>
       </c>
-      <c r="H10" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="18" t="n">
+      <c r="H10" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I10" s="26" t="n">
         <f aca="false">RANK(G10,$G$6:$G$11,0)+COUNTIF($G$6:G10,G10)-1</f>
         <v>5</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="26" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I10,$F$6:$F$11)</f>
         <v>63</v>
       </c>
-      <c r="K10" s="19" t="str">
+      <c r="K10" s="27" t="str">
         <f aca="false">IF(J10&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L10" s="20" t="n">
+      <c r="L10" s="28" t="n">
         <f aca="false">RANK(C10,$C$6:$C$11,0)+COUNTIF($C$6:C10,C10)-1</f>
         <v>2</v>
       </c>
-      <c r="M10" s="20" t="n">
+      <c r="M10" s="28" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L10,$F$6:$F$11)</f>
         <v>37</v>
       </c>
-      <c r="N10" s="21" t="str">
+      <c r="N10" s="29" t="str">
         <f aca="false">IF(M10&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O10" s="22" t="n">
+      <c r="O10" s="30" t="n">
         <f aca="false">RANK(F10,$F$6:$F$11,1)+COUNTIF($F$6:F10,F10)-1</f>
         <v>6</v>
       </c>
-      <c r="P10" s="22" t="n">
+      <c r="P10" s="30" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O10,$F$6:$F$11)</f>
         <v>88</v>
       </c>
-      <c r="Q10" s="23" t="str">
+      <c r="Q10" s="31" t="str">
         <f aca="false">IF(P10&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="32" t="n">
         <f aca="false">D11+E11</f>
         <v>8</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="33" t="n">
         <f aca="false">IFERROR(C11/F11,0)</f>
         <v>3.75</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" s="18" t="n">
+      <c r="H11" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I11" s="26" t="n">
         <f aca="false">RANK(G11,$G$6:$G$11,0)+COUNTIF($G$6:G11,G11)-1</f>
         <v>4</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="26" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I11,$F$6:$F$11)</f>
         <v>36</v>
       </c>
-      <c r="K11" s="19" t="str">
+      <c r="K11" s="27" t="str">
         <f aca="false">IF(J11&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="L11" s="28" t="n">
         <f aca="false">RANK(C11,$C$6:$C$11,0)+COUNTIF($C$6:C11,C11)-1</f>
         <v>6</v>
       </c>
-      <c r="M11" s="20" t="n">
+      <c r="M11" s="28" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L11,$F$6:$F$11)</f>
         <v>88</v>
       </c>
-      <c r="N11" s="21" t="str">
+      <c r="N11" s="29" t="str">
         <f aca="false">IF(M11&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="O11" s="22" t="n">
+      <c r="O11" s="30" t="n">
         <f aca="false">RANK(F11,$F$6:$F$11,1)+COUNTIF($F$6:F11,F11)-1</f>
         <v>2</v>
       </c>
-      <c r="P11" s="22" t="n">
+      <c r="P11" s="30" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O11,$F$6:$F$11)</f>
         <v>13</v>
       </c>
-      <c r="Q11" s="23" t="str">
+      <c r="Q11" s="31" t="str">
         <f aca="false">IF(P11&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="27" t="n">
+      <c r="A12" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="37" t="n">
         <f aca="false">SUMIF(H6:H11,"Y",F6:F11)</f>
         <v>63</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="38" t="n">
         <f aca="false">SUMIF(H6:H11,"Y",C6:C11)</f>
         <v>326</v>
       </c>
-      <c r="H12" s="29" t="s">
-        <v>169</v>
+      <c r="H12" s="39" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="A13" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
       <c r="F13" s="27" t="n">
         <f aca="false">SUMIF(K6:K11,"Y",F6:F11)</f>
         <v>63</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">SUMIF(K6:K11,"Y",C6:C11)</f>
         <v>326</v>
       </c>
-      <c r="H13" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="M13" s="21" t="n">
+      <c r="H13" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="M13" s="29" t="n">
         <f aca="false">SUMIF(N6:N11,"Y",F6:F11)</f>
         <v>80</v>
       </c>
-      <c r="N13" s="30" t="n">
+      <c r="N13" s="42" t="n">
         <f aca="false">SUMIF(N6:N11,"Y",C6:C11)</f>
         <v>374</v>
       </c>
-      <c r="P13" s="23" t="n">
+      <c r="P13" s="31" t="n">
         <f aca="false">SUMIF(Q6:Q11,"Y",F6:F11)</f>
         <v>61</v>
       </c>
-      <c r="Q13" s="31" t="n">
+      <c r="Q13" s="43" t="n">
         <f aca="false">SUMIF(Q6:Q11,"Y",C6:C11)</f>
         <v>316</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="A14" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="A15" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
+      <c r="A16" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="415.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4978,139 +6033,142 @@
       <c r="Q18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
+      <c r="A19" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>181</v>
+      <c r="A20" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D21" s="18" t="n">
+      <c r="A21" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" s="26" t="n">
         <f aca="false">F13</f>
         <v>63</v>
       </c>
-      <c r="E21" s="33" t="n">
+      <c r="E21" s="45" t="n">
         <f aca="false">G13</f>
         <v>326</v>
       </c>
-      <c r="F21" s="33" t="n">
+      <c r="F21" s="45" t="n">
         <f aca="false">IFERROR(G13/F13,0)</f>
         <v>5.17460317460318</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="20" t="n">
+      <c r="A22" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="D22" s="28" t="n">
         <f aca="false">M13</f>
         <v>80</v>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="48" t="n">
         <f aca="false">N13</f>
         <v>374</v>
       </c>
-      <c r="F22" s="35" t="n">
+      <c r="F22" s="48" t="n">
         <f aca="false">IFERROR(N13/M13,0)</f>
         <v>4.675</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="C23" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="D23" s="22" t="n">
+      <c r="A23" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="30" t="n">
         <f aca="false">P13</f>
         <v>61</v>
       </c>
-      <c r="E23" s="38" t="n">
+      <c r="E23" s="50" t="n">
         <f aca="false">Q13</f>
         <v>316</v>
       </c>
-      <c r="F23" s="38" t="n">
+      <c r="F23" s="50" t="n">
         <f aca="false">IFERROR(Q13/P13,0)</f>
         <v>5.18032786885246</v>
       </c>
     </row>
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-    </row>
+      <c r="A25" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="482.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A13:E13"/>
@@ -5129,80 +6187,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="95"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>